--- a/mom/docs/forms/frm-500-production/FRM-515_Tool_Change_Verification_Record.xlsx
+++ b/mom/docs/forms/frm-500-production/FRM-515_Tool_Change_Verification_Record.xlsx
@@ -3698,7 +3698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="522">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4928,14 +4928,18 @@
     <xf numFmtId="0" fontId="86" fillId="55" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="52" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="54" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="52" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="49" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="80" fillId="47" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5066,6 +5070,52 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Vị trí / mã dao
+Số pocket hoặc mã dao trên máy.</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
+      <text>
+        <t>Mô tả dao
+Loại, mảnh, hình học dao.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Lý do thay dao
+Mòn / gãy vỡ / theo lịch / chất lượng bề mặt.</t>
+      </text>
+    </comment>
+    <comment ref="U12" authorId="0" shapeId="0">
+      <text>
+        <t>Tham chiếu
+FRM-513 — Nhật ký tuổi thọ dao.</t>
+      </text>
+    </comment>
+    <comment ref="AF17" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS / HOLD / FAIL — chọn từ danh sách.</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Kiểm tra chi tiết đầu
+Bắt buộc — thay dao mà không đo chi tiết đầu là vi phạm quy trình.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5390,7 +5440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BS41"/>
+  <dimension ref="A2:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -5636,7 +5686,7 @@
       <c r="AN6" s="272" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="523" t="n"/>
+      <c r="A7" s="521" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -5680,7 +5730,7 @@
     <row r="8" ht="17" customHeight="1" s="264">
       <c r="A8" s="470" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.  REFERENCE INFORMATION</t>
+          <t xml:space="preserve">  1.  JOB &amp; TOOL-CHANGE HEADER</t>
         </is>
       </c>
       <c r="B8" s="471" t="n"/>
@@ -5850,7 +5900,7 @@
       <c r="T11" s="482" t="n"/>
       <c r="U11" s="484" t="inlineStr">
         <is>
-          <t>Reason for Change</t>
+          <t>Tool Description</t>
         </is>
       </c>
       <c r="V11" s="481" t="n"/>
@@ -5876,7 +5926,7 @@
     <row r="12" ht="20" customHeight="1" s="264">
       <c r="A12" s="480" t="inlineStr">
         <is>
-          <t>Operator</t>
+          <t>Reason for Change</t>
         </is>
       </c>
       <c r="B12" s="481" t="n"/>
@@ -5900,7 +5950,7 @@
       <c r="T12" s="482" t="n"/>
       <c r="U12" s="484" t="inlineStr">
         <is>
-          <t>QC Verifier</t>
+          <t>Linked FRM-513 Tool Life</t>
         </is>
       </c>
       <c r="V12" s="481" t="n"/>
@@ -5924,269 +5974,262 @@
       <c r="AN12" s="486" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="264">
-      <c r="A13" s="487" t="inlineStr">
-        <is>
-          <t>Date / Time</t>
-        </is>
-      </c>
-      <c r="B13" s="488" t="n"/>
-      <c r="C13" s="488" t="n"/>
-      <c r="D13" s="488" t="n"/>
-      <c r="E13" s="488" t="n"/>
-      <c r="F13" s="488" t="n"/>
-      <c r="G13" s="489" t="n"/>
-      <c r="H13" s="490" t="n"/>
-      <c r="I13" s="488" t="n"/>
-      <c r="J13" s="488" t="n"/>
-      <c r="K13" s="488" t="n"/>
-      <c r="L13" s="488" t="n"/>
-      <c r="M13" s="488" t="n"/>
-      <c r="N13" s="488" t="n"/>
-      <c r="O13" s="488" t="n"/>
-      <c r="P13" s="488" t="n"/>
-      <c r="Q13" s="488" t="n"/>
-      <c r="R13" s="488" t="n"/>
-      <c r="S13" s="488" t="n"/>
-      <c r="T13" s="489" t="n"/>
-      <c r="U13" s="491" t="inlineStr">
-        <is>
-          <t>Linked FRM-513 Tool Life</t>
-        </is>
-      </c>
-      <c r="V13" s="488" t="n"/>
-      <c r="W13" s="488" t="n"/>
-      <c r="X13" s="488" t="n"/>
-      <c r="Y13" s="488" t="n"/>
-      <c r="Z13" s="488" t="n"/>
-      <c r="AA13" s="489" t="n"/>
-      <c r="AB13" s="492" t="n"/>
-      <c r="AC13" s="488" t="n"/>
-      <c r="AD13" s="488" t="n"/>
-      <c r="AE13" s="488" t="n"/>
-      <c r="AF13" s="488" t="n"/>
-      <c r="AG13" s="488" t="n"/>
-      <c r="AH13" s="488" t="n"/>
-      <c r="AI13" s="488" t="n"/>
-      <c r="AJ13" s="488" t="n"/>
-      <c r="AK13" s="488" t="n"/>
-      <c r="AL13" s="488" t="n"/>
-      <c r="AM13" s="488" t="n"/>
-      <c r="AN13" s="493" t="n"/>
+      <c r="A13" s="480" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="B13" s="481" t="n"/>
+      <c r="C13" s="481" t="n"/>
+      <c r="D13" s="481" t="n"/>
+      <c r="E13" s="481" t="n"/>
+      <c r="F13" s="481" t="n"/>
+      <c r="G13" s="482" t="n"/>
+      <c r="H13" s="483" t="n"/>
+      <c r="I13" s="481" t="n"/>
+      <c r="J13" s="481" t="n"/>
+      <c r="K13" s="481" t="n"/>
+      <c r="L13" s="481" t="n"/>
+      <c r="M13" s="481" t="n"/>
+      <c r="N13" s="481" t="n"/>
+      <c r="O13" s="481" t="n"/>
+      <c r="P13" s="481" t="n"/>
+      <c r="Q13" s="481" t="n"/>
+      <c r="R13" s="481" t="n"/>
+      <c r="S13" s="481" t="n"/>
+      <c r="T13" s="482" t="n"/>
+      <c r="U13" s="484" t="inlineStr">
+        <is>
+          <t>QC Verifier</t>
+        </is>
+      </c>
+      <c r="V13" s="481" t="n"/>
+      <c r="W13" s="481" t="n"/>
+      <c r="X13" s="481" t="n"/>
+      <c r="Y13" s="481" t="n"/>
+      <c r="Z13" s="481" t="n"/>
+      <c r="AA13" s="482" t="n"/>
+      <c r="AB13" s="485" t="n"/>
+      <c r="AC13" s="481" t="n"/>
+      <c r="AD13" s="481" t="n"/>
+      <c r="AE13" s="481" t="n"/>
+      <c r="AF13" s="481" t="n"/>
+      <c r="AG13" s="481" t="n"/>
+      <c r="AH13" s="481" t="n"/>
+      <c r="AI13" s="481" t="n"/>
+      <c r="AJ13" s="481" t="n"/>
+      <c r="AK13" s="481" t="n"/>
+      <c r="AL13" s="481" t="n"/>
+      <c r="AM13" s="481" t="n"/>
+      <c r="AN13" s="486" t="n"/>
     </row>
-    <row r="14" ht="4" customHeight="1" s="264">
-      <c r="A14" s="523" t="n"/>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="26" t="n"/>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="26" t="n"/>
-      <c r="O14" s="26" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="26" t="n"/>
-      <c r="R14" s="26" t="n"/>
-      <c r="S14" s="26" t="n"/>
-      <c r="T14" s="26" t="n"/>
-      <c r="U14" s="26" t="n"/>
-      <c r="V14" s="26" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="26" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="26" t="n"/>
-      <c r="AB14" s="26" t="n"/>
-      <c r="AC14" s="26" t="n"/>
-      <c r="AD14" s="26" t="n"/>
-      <c r="AE14" s="26" t="n"/>
-      <c r="AF14" s="26" t="n"/>
-      <c r="AG14" s="26" t="n"/>
-      <c r="AH14" s="26" t="n"/>
-      <c r="AI14" s="26" t="n"/>
-      <c r="AJ14" s="26" t="n"/>
-      <c r="AK14" s="26" t="n"/>
-      <c r="AL14" s="26" t="n"/>
-      <c r="AM14" s="26" t="n"/>
-      <c r="AN14" s="26" t="n"/>
+    <row r="14" ht="20" customHeight="1" s="264">
+      <c r="A14" s="487" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B14" s="488" t="n"/>
+      <c r="C14" s="488" t="n"/>
+      <c r="D14" s="488" t="n"/>
+      <c r="E14" s="488" t="n"/>
+      <c r="F14" s="488" t="n"/>
+      <c r="G14" s="489" t="n"/>
+      <c r="H14" s="490" t="n"/>
+      <c r="I14" s="488" t="n"/>
+      <c r="J14" s="488" t="n"/>
+      <c r="K14" s="488" t="n"/>
+      <c r="L14" s="488" t="n"/>
+      <c r="M14" s="488" t="n"/>
+      <c r="N14" s="488" t="n"/>
+      <c r="O14" s="488" t="n"/>
+      <c r="P14" s="488" t="n"/>
+      <c r="Q14" s="488" t="n"/>
+      <c r="R14" s="488" t="n"/>
+      <c r="S14" s="488" t="n"/>
+      <c r="T14" s="489" t="n"/>
+      <c r="U14" s="491" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="V14" s="488" t="n"/>
+      <c r="W14" s="488" t="n"/>
+      <c r="X14" s="488" t="n"/>
+      <c r="Y14" s="488" t="n"/>
+      <c r="Z14" s="488" t="n"/>
+      <c r="AA14" s="489" t="n"/>
+      <c r="AB14" s="492" t="n"/>
+      <c r="AC14" s="488" t="n"/>
+      <c r="AD14" s="488" t="n"/>
+      <c r="AE14" s="488" t="n"/>
+      <c r="AF14" s="488" t="n"/>
+      <c r="AG14" s="488" t="n"/>
+      <c r="AH14" s="488" t="n"/>
+      <c r="AI14" s="488" t="n"/>
+      <c r="AJ14" s="488" t="n"/>
+      <c r="AK14" s="488" t="n"/>
+      <c r="AL14" s="488" t="n"/>
+      <c r="AM14" s="488" t="n"/>
+      <c r="AN14" s="493" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="264">
-      <c r="A15" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2.  TOOL-CHANGE VERIFICATION CHECKLIST</t>
-        </is>
-      </c>
-      <c r="B15" s="471" t="n"/>
-      <c r="C15" s="471" t="n"/>
-      <c r="D15" s="471" t="n"/>
-      <c r="E15" s="471" t="n"/>
-      <c r="F15" s="471" t="n"/>
-      <c r="G15" s="471" t="n"/>
-      <c r="H15" s="471" t="n"/>
-      <c r="I15" s="471" t="n"/>
-      <c r="J15" s="471" t="n"/>
-      <c r="K15" s="471" t="n"/>
-      <c r="L15" s="471" t="n"/>
-      <c r="M15" s="471" t="n"/>
-      <c r="N15" s="471" t="n"/>
-      <c r="O15" s="471" t="n"/>
-      <c r="P15" s="471" t="n"/>
-      <c r="Q15" s="471" t="n"/>
-      <c r="R15" s="471" t="n"/>
-      <c r="S15" s="471" t="n"/>
-      <c r="T15" s="471" t="n"/>
-      <c r="U15" s="471" t="n"/>
-      <c r="V15" s="471" t="n"/>
-      <c r="W15" s="471" t="n"/>
-      <c r="X15" s="471" t="n"/>
-      <c r="Y15" s="471" t="n"/>
-      <c r="Z15" s="471" t="n"/>
-      <c r="AA15" s="471" t="n"/>
-      <c r="AB15" s="471" t="n"/>
-      <c r="AC15" s="471" t="n"/>
-      <c r="AD15" s="471" t="n"/>
-      <c r="AE15" s="471" t="n"/>
-      <c r="AF15" s="471" t="n"/>
-      <c r="AG15" s="471" t="n"/>
-      <c r="AH15" s="471" t="n"/>
-      <c r="AI15" s="471" t="n"/>
-      <c r="AJ15" s="471" t="n"/>
-      <c r="AK15" s="471" t="n"/>
-      <c r="AL15" s="471" t="n"/>
-      <c r="AM15" s="471" t="n"/>
-      <c r="AN15" s="472" t="n"/>
+    <row r="15" ht="4" customHeight="1" s="264">
+      <c r="A15" s="521" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="26" t="n"/>
+      <c r="J15" s="26" t="n"/>
+      <c r="K15" s="26" t="n"/>
+      <c r="L15" s="26" t="n"/>
+      <c r="M15" s="26" t="n"/>
+      <c r="N15" s="26" t="n"/>
+      <c r="O15" s="26" t="n"/>
+      <c r="P15" s="26" t="n"/>
+      <c r="Q15" s="26" t="n"/>
+      <c r="R15" s="26" t="n"/>
+      <c r="S15" s="26" t="n"/>
+      <c r="T15" s="26" t="n"/>
+      <c r="U15" s="26" t="n"/>
+      <c r="V15" s="26" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="26" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="26" t="n"/>
+      <c r="AB15" s="26" t="n"/>
+      <c r="AC15" s="26" t="n"/>
+      <c r="AD15" s="26" t="n"/>
+      <c r="AE15" s="26" t="n"/>
+      <c r="AF15" s="26" t="n"/>
+      <c r="AG15" s="26" t="n"/>
+      <c r="AH15" s="26" t="n"/>
+      <c r="AI15" s="26" t="n"/>
+      <c r="AJ15" s="26" t="n"/>
+      <c r="AK15" s="26" t="n"/>
+      <c r="AL15" s="26" t="n"/>
+      <c r="AM15" s="26" t="n"/>
+      <c r="AN15" s="26" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1" s="264">
-      <c r="A16" s="494" t="inlineStr">
+      <c r="A16" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2.  TOOL-CHANGE VERIFICATION CHECKLIST</t>
+        </is>
+      </c>
+      <c r="B16" s="471" t="n"/>
+      <c r="C16" s="471" t="n"/>
+      <c r="D16" s="471" t="n"/>
+      <c r="E16" s="471" t="n"/>
+      <c r="F16" s="471" t="n"/>
+      <c r="G16" s="471" t="n"/>
+      <c r="H16" s="471" t="n"/>
+      <c r="I16" s="471" t="n"/>
+      <c r="J16" s="471" t="n"/>
+      <c r="K16" s="471" t="n"/>
+      <c r="L16" s="471" t="n"/>
+      <c r="M16" s="471" t="n"/>
+      <c r="N16" s="471" t="n"/>
+      <c r="O16" s="471" t="n"/>
+      <c r="P16" s="471" t="n"/>
+      <c r="Q16" s="471" t="n"/>
+      <c r="R16" s="471" t="n"/>
+      <c r="S16" s="471" t="n"/>
+      <c r="T16" s="471" t="n"/>
+      <c r="U16" s="471" t="n"/>
+      <c r="V16" s="471" t="n"/>
+      <c r="W16" s="471" t="n"/>
+      <c r="X16" s="471" t="n"/>
+      <c r="Y16" s="471" t="n"/>
+      <c r="Z16" s="471" t="n"/>
+      <c r="AA16" s="471" t="n"/>
+      <c r="AB16" s="471" t="n"/>
+      <c r="AC16" s="471" t="n"/>
+      <c r="AD16" s="471" t="n"/>
+      <c r="AE16" s="471" t="n"/>
+      <c r="AF16" s="471" t="n"/>
+      <c r="AG16" s="471" t="n"/>
+      <c r="AH16" s="471" t="n"/>
+      <c r="AI16" s="471" t="n"/>
+      <c r="AJ16" s="471" t="n"/>
+      <c r="AK16" s="471" t="n"/>
+      <c r="AL16" s="471" t="n"/>
+      <c r="AM16" s="471" t="n"/>
+      <c r="AN16" s="472" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1" s="264">
+      <c r="A17" s="494" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="475" t="n"/>
-      <c r="C16" s="495" t="inlineStr">
+      <c r="B17" s="475" t="n"/>
+      <c r="C17" s="495" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D16" s="474" t="n"/>
-      <c r="E16" s="475" t="n"/>
-      <c r="F16" s="495" t="inlineStr">
-        <is>
-          <t>Tool-Change Verification Item</t>
-        </is>
-      </c>
-      <c r="G16" s="474" t="n"/>
-      <c r="H16" s="474" t="n"/>
-      <c r="I16" s="474" t="n"/>
-      <c r="J16" s="474" t="n"/>
-      <c r="K16" s="474" t="n"/>
-      <c r="L16" s="474" t="n"/>
-      <c r="M16" s="474" t="n"/>
-      <c r="N16" s="474" t="n"/>
-      <c r="O16" s="474" t="n"/>
-      <c r="P16" s="474" t="n"/>
-      <c r="Q16" s="474" t="n"/>
-      <c r="R16" s="474" t="n"/>
-      <c r="S16" s="474" t="n"/>
-      <c r="T16" s="474" t="n"/>
-      <c r="U16" s="475" t="n"/>
-      <c r="V16" s="495" t="inlineStr">
-        <is>
-          <t>Acceptance / Control Rule</t>
-        </is>
-      </c>
-      <c r="W16" s="474" t="n"/>
-      <c r="X16" s="474" t="n"/>
-      <c r="Y16" s="474" t="n"/>
-      <c r="Z16" s="474" t="n"/>
-      <c r="AA16" s="474" t="n"/>
-      <c r="AB16" s="474" t="n"/>
-      <c r="AC16" s="474" t="n"/>
-      <c r="AD16" s="474" t="n"/>
-      <c r="AE16" s="475" t="n"/>
-      <c r="AF16" s="495" t="inlineStr">
+      <c r="D17" s="474" t="n"/>
+      <c r="E17" s="475" t="n"/>
+      <c r="F17" s="495" t="inlineStr">
+        <is>
+          <t>Verification Item</t>
+        </is>
+      </c>
+      <c r="G17" s="474" t="n"/>
+      <c r="H17" s="474" t="n"/>
+      <c r="I17" s="474" t="n"/>
+      <c r="J17" s="474" t="n"/>
+      <c r="K17" s="474" t="n"/>
+      <c r="L17" s="474" t="n"/>
+      <c r="M17" s="474" t="n"/>
+      <c r="N17" s="474" t="n"/>
+      <c r="O17" s="474" t="n"/>
+      <c r="P17" s="474" t="n"/>
+      <c r="Q17" s="474" t="n"/>
+      <c r="R17" s="474" t="n"/>
+      <c r="S17" s="474" t="n"/>
+      <c r="T17" s="474" t="n"/>
+      <c r="U17" s="475" t="n"/>
+      <c r="V17" s="495" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="W17" s="474" t="n"/>
+      <c r="X17" s="474" t="n"/>
+      <c r="Y17" s="474" t="n"/>
+      <c r="Z17" s="474" t="n"/>
+      <c r="AA17" s="474" t="n"/>
+      <c r="AB17" s="474" t="n"/>
+      <c r="AC17" s="474" t="n"/>
+      <c r="AD17" s="474" t="n"/>
+      <c r="AE17" s="475" t="n"/>
+      <c r="AF17" s="495" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG16" s="474" t="n"/>
-      <c r="AH16" s="474" t="n"/>
-      <c r="AI16" s="475" t="n"/>
-      <c r="AJ16" s="496" t="inlineStr">
+      <c r="AG17" s="474" t="n"/>
+      <c r="AH17" s="474" t="n"/>
+      <c r="AI17" s="475" t="n"/>
+      <c r="AJ17" s="496" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK16" s="474" t="n"/>
-      <c r="AL16" s="474" t="n"/>
-      <c r="AM16" s="474" t="n"/>
-      <c r="AN16" s="479" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
-        <v/>
-      </c>
-      <c r="B17" s="482" t="n"/>
-      <c r="C17" s="498" t="inlineStr">
-        <is>
-          <t>TOOL</t>
-        </is>
-      </c>
-      <c r="D17" s="481" t="n"/>
-      <c r="E17" s="482" t="n"/>
-      <c r="F17" s="499" t="inlineStr">
-        <is>
-          <t>Removed tool matches the released tool list.</t>
-        </is>
-      </c>
-      <c r="G17" s="481" t="n"/>
-      <c r="H17" s="481" t="n"/>
-      <c r="I17" s="481" t="n"/>
-      <c r="J17" s="481" t="n"/>
-      <c r="K17" s="481" t="n"/>
-      <c r="L17" s="481" t="n"/>
-      <c r="M17" s="481" t="n"/>
-      <c r="N17" s="481" t="n"/>
-      <c r="O17" s="481" t="n"/>
-      <c r="P17" s="481" t="n"/>
-      <c r="Q17" s="481" t="n"/>
-      <c r="R17" s="481" t="n"/>
-      <c r="S17" s="481" t="n"/>
-      <c r="T17" s="481" t="n"/>
-      <c r="U17" s="482" t="n"/>
-      <c r="V17" s="500" t="inlineStr">
-        <is>
-          <t>Pocket/ID reconciled to FRM-302 tool list.</t>
-        </is>
-      </c>
-      <c r="W17" s="481" t="n"/>
-      <c r="X17" s="481" t="n"/>
-      <c r="Y17" s="481" t="n"/>
-      <c r="Z17" s="481" t="n"/>
-      <c r="AA17" s="481" t="n"/>
-      <c r="AB17" s="481" t="n"/>
-      <c r="AC17" s="481" t="n"/>
-      <c r="AD17" s="481" t="n"/>
-      <c r="AE17" s="482" t="n"/>
-      <c r="AF17" s="501" t="n"/>
-      <c r="AG17" s="481" t="n"/>
-      <c r="AH17" s="481" t="n"/>
-      <c r="AI17" s="482" t="n"/>
-      <c r="AJ17" s="502" t="n"/>
-      <c r="AK17" s="481" t="n"/>
-      <c r="AL17" s="481" t="n"/>
-      <c r="AM17" s="481" t="n"/>
-      <c r="AN17" s="486" t="n"/>
+      <c r="AK17" s="474" t="n"/>
+      <c r="AL17" s="474" t="n"/>
+      <c r="AM17" s="474" t="n"/>
+      <c r="AN17" s="479" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
       <c r="A18" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B18" s="482" t="n"/>
@@ -6197,9 +6240,9 @@
       </c>
       <c r="D18" s="481" t="n"/>
       <c r="E18" s="482" t="n"/>
-      <c r="F18" s="503" t="inlineStr">
-        <is>
-          <t>New tool is correct type, grade and geometry.</t>
+      <c r="F18" s="499" t="inlineStr">
+        <is>
+          <t>Removed tool matches the released tool list.</t>
         </is>
       </c>
       <c r="G18" s="481" t="n"/>
@@ -6219,7 +6262,7 @@
       <c r="U18" s="482" t="n"/>
       <c r="V18" s="500" t="inlineStr">
         <is>
-          <t>Insert/holder verified against tool list spec.</t>
+          <t>Pocket / ID reconciled to FRM-302.</t>
         </is>
       </c>
       <c r="W18" s="481" t="n"/>
@@ -6243,7 +6286,7 @@
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
       <c r="A19" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B19" s="482" t="n"/>
@@ -6254,9 +6297,9 @@
       </c>
       <c r="D19" s="481" t="n"/>
       <c r="E19" s="482" t="n"/>
-      <c r="F19" s="499" t="inlineStr">
-        <is>
-          <t>Tool length / offset set and verified at presetter.</t>
+      <c r="F19" s="503" t="inlineStr">
+        <is>
+          <t>New tool is correct type, grade and geometry.</t>
         </is>
       </c>
       <c r="G19" s="481" t="n"/>
@@ -6276,7 +6319,7 @@
       <c r="U19" s="482" t="n"/>
       <c r="V19" s="500" t="inlineStr">
         <is>
-          <t>Presetter or touch-off value recorded.</t>
+          <t>Insert / holder verified to tool-list spec.</t>
         </is>
       </c>
       <c r="W19" s="481" t="n"/>
@@ -6300,20 +6343,20 @@
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
       <c r="A20" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B20" s="482" t="n"/>
-      <c r="C20" s="504" t="inlineStr">
-        <is>
-          <t>GAGE</t>
+      <c r="C20" s="498" t="inlineStr">
+        <is>
+          <t>TOOL</t>
         </is>
       </c>
       <c r="D20" s="481" t="n"/>
       <c r="E20" s="482" t="n"/>
-      <c r="F20" s="503" t="inlineStr">
-        <is>
-          <t>Tool offset value entered into the correct register.</t>
+      <c r="F20" s="499" t="inlineStr">
+        <is>
+          <t>Tool length / offset set and verified at presetter.</t>
         </is>
       </c>
       <c r="G20" s="481" t="n"/>
@@ -6333,7 +6376,7 @@
       <c r="U20" s="482" t="n"/>
       <c r="V20" s="500" t="inlineStr">
         <is>
-          <t>Offset register reconciled on control.</t>
+          <t>Presetter or touch-off value recorded.</t>
         </is>
       </c>
       <c r="W20" s="481" t="n"/>
@@ -6357,20 +6400,20 @@
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
       <c r="A21" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B21" s="482" t="n"/>
-      <c r="C21" s="505" t="inlineStr">
-        <is>
-          <t>OPS</t>
+      <c r="C21" s="504" t="inlineStr">
+        <is>
+          <t>GAGE</t>
         </is>
       </c>
       <c r="D21" s="481" t="n"/>
       <c r="E21" s="482" t="n"/>
-      <c r="F21" s="499" t="inlineStr">
-        <is>
-          <t>Wear compensation reset for the new tool.</t>
+      <c r="F21" s="503" t="inlineStr">
+        <is>
+          <t>Tool offset entered into the correct register.</t>
         </is>
       </c>
       <c r="G21" s="481" t="n"/>
@@ -6390,7 +6433,7 @@
       <c r="U21" s="482" t="n"/>
       <c r="V21" s="500" t="inlineStr">
         <is>
-          <t>Wear/comp value zeroed or set to baseline.</t>
+          <t>Offset register reconciled on the control.</t>
         </is>
       </c>
       <c r="W21" s="481" t="n"/>
@@ -6414,20 +6457,20 @@
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
       <c r="A22" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B22" s="482" t="n"/>
-      <c r="C22" s="506" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C22" s="505" t="inlineStr">
+        <is>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D22" s="481" t="n"/>
       <c r="E22" s="482" t="n"/>
-      <c r="F22" s="503" t="inlineStr">
-        <is>
-          <t>First piece after change measured on CTQ features.</t>
+      <c r="F22" s="499" t="inlineStr">
+        <is>
+          <t>Wear compensation reset for the new tool.</t>
         </is>
       </c>
       <c r="G22" s="481" t="n"/>
@@ -6447,7 +6490,7 @@
       <c r="U22" s="482" t="n"/>
       <c r="V22" s="500" t="inlineStr">
         <is>
-          <t>Dimensions logged on FRM-622.</t>
+          <t>Wear / comp value zeroed or set to baseline.</t>
         </is>
       </c>
       <c r="W22" s="481" t="n"/>
@@ -6471,20 +6514,20 @@
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
       <c r="A23" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B23" s="482" t="n"/>
-      <c r="C23" s="506" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C23" s="498" t="inlineStr">
+        <is>
+          <t>TOOL</t>
         </is>
       </c>
       <c r="D23" s="481" t="n"/>
       <c r="E23" s="482" t="n"/>
-      <c r="F23" s="499" t="inlineStr">
-        <is>
-          <t>Post-change readings within tolerance band.</t>
+      <c r="F23" s="503" t="inlineStr">
+        <is>
+          <t>Tool runout / projection within limit.</t>
         </is>
       </c>
       <c r="G23" s="481" t="n"/>
@@ -6504,7 +6547,7 @@
       <c r="U23" s="482" t="n"/>
       <c r="V23" s="500" t="inlineStr">
         <is>
-          <t>All CTQ within drawing limits.</t>
+          <t>Checked at holder; no excessive runout.</t>
         </is>
       </c>
       <c r="W23" s="481" t="n"/>
@@ -6528,20 +6571,20 @@
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
       <c r="A24" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B24" s="482" t="n"/>
-      <c r="C24" s="498" t="inlineStr">
-        <is>
-          <t>TOOL</t>
+      <c r="C24" s="506" t="inlineStr">
+        <is>
+          <t>QUA</t>
         </is>
       </c>
       <c r="D24" s="481" t="n"/>
       <c r="E24" s="482" t="n"/>
-      <c r="F24" s="503" t="inlineStr">
-        <is>
-          <t>Removed tool tagged and dispositioned.</t>
+      <c r="F24" s="499" t="inlineStr">
+        <is>
+          <t>First piece after change measured on CTQ features.</t>
         </is>
       </c>
       <c r="G24" s="481" t="n"/>
@@ -6561,7 +6604,7 @@
       <c r="U24" s="482" t="n"/>
       <c r="V24" s="500" t="inlineStr">
         <is>
-          <t>Re-grind / scrap / return decision recorded.</t>
+          <t>Dimensions logged on FRM-622.</t>
         </is>
       </c>
       <c r="W24" s="481" t="n"/>
@@ -6585,20 +6628,20 @@
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
       <c r="A25" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B25" s="482" t="n"/>
-      <c r="C25" s="505" t="inlineStr">
-        <is>
-          <t>OPS</t>
+      <c r="C25" s="506" t="inlineStr">
+        <is>
+          <t>QUA</t>
         </is>
       </c>
       <c r="D25" s="481" t="n"/>
       <c r="E25" s="482" t="n"/>
-      <c r="F25" s="499" t="inlineStr">
-        <is>
-          <t>Tool life counter reset on the controller.</t>
+      <c r="F25" s="503" t="inlineStr">
+        <is>
+          <t>Post-change readings within tolerance band.</t>
         </is>
       </c>
       <c r="G25" s="481" t="n"/>
@@ -6618,7 +6661,7 @@
       <c r="U25" s="482" t="n"/>
       <c r="V25" s="500" t="inlineStr">
         <is>
-          <t>FRM-513 tool-life log updated.</t>
+          <t>All CTQ within drawing limits.</t>
         </is>
       </c>
       <c r="W25" s="481" t="n"/>
@@ -6642,20 +6685,20 @@
     </row>
     <row r="26" ht="20" customHeight="1" s="264">
       <c r="A26" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B26" s="482" t="n"/>
-      <c r="C26" s="505" t="inlineStr">
-        <is>
-          <t>OPS</t>
+      <c r="C26" s="506" t="inlineStr">
+        <is>
+          <t>QUA</t>
         </is>
       </c>
       <c r="D26" s="481" t="n"/>
       <c r="E26" s="482" t="n"/>
-      <c r="F26" s="503" t="inlineStr">
-        <is>
-          <t>Run condition after tool change is explicit.</t>
+      <c r="F26" s="499" t="inlineStr">
+        <is>
+          <t>Surface finish / burr acceptable after change.</t>
         </is>
       </c>
       <c r="G26" s="481" t="n"/>
@@ -6675,7 +6718,7 @@
       <c r="U26" s="482" t="n"/>
       <c r="V26" s="500" t="inlineStr">
         <is>
-          <t>Pass-to-run or hold decision visible.</t>
+          <t>Visual + Ra check per drawing.</t>
         </is>
       </c>
       <c r="W26" s="481" t="n"/>
@@ -6699,14 +6742,22 @@
     </row>
     <row r="27" ht="20" customHeight="1" s="264">
       <c r="A27" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B27" s="482" t="n"/>
-      <c r="C27" s="507" t="n"/>
+      <c r="C27" s="498" t="inlineStr">
+        <is>
+          <t>TOOL</t>
+        </is>
+      </c>
       <c r="D27" s="481" t="n"/>
       <c r="E27" s="482" t="n"/>
-      <c r="F27" s="508" t="n"/>
+      <c r="F27" s="503" t="inlineStr">
+        <is>
+          <t>Removed tool tagged and dispositioned.</t>
+        </is>
+      </c>
       <c r="G27" s="481" t="n"/>
       <c r="H27" s="481" t="n"/>
       <c r="I27" s="481" t="n"/>
@@ -6722,7 +6773,11 @@
       <c r="S27" s="481" t="n"/>
       <c r="T27" s="481" t="n"/>
       <c r="U27" s="482" t="n"/>
-      <c r="V27" s="507" t="n"/>
+      <c r="V27" s="500" t="inlineStr">
+        <is>
+          <t>Re-grind / scrap / return decision recorded.</t>
+        </is>
+      </c>
       <c r="W27" s="481" t="n"/>
       <c r="X27" s="481" t="n"/>
       <c r="Y27" s="481" t="n"/>
@@ -6744,14 +6799,22 @@
     </row>
     <row r="28" ht="20" customHeight="1" s="264">
       <c r="A28" s="497">
-        <f>ROW()-ROW($A$17)+1</f>
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B28" s="482" t="n"/>
-      <c r="C28" s="507" t="n"/>
+      <c r="C28" s="505" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
       <c r="D28" s="481" t="n"/>
       <c r="E28" s="482" t="n"/>
-      <c r="F28" s="509" t="n"/>
+      <c r="F28" s="499" t="inlineStr">
+        <is>
+          <t>Tool life counter reset on the controller.</t>
+        </is>
+      </c>
       <c r="G28" s="481" t="n"/>
       <c r="H28" s="481" t="n"/>
       <c r="I28" s="481" t="n"/>
@@ -6767,7 +6830,11 @@
       <c r="S28" s="481" t="n"/>
       <c r="T28" s="481" t="n"/>
       <c r="U28" s="482" t="n"/>
-      <c r="V28" s="507" t="n"/>
+      <c r="V28" s="500" t="inlineStr">
+        <is>
+          <t>FRM-513 tool-life log updated.</t>
+        </is>
+      </c>
       <c r="W28" s="481" t="n"/>
       <c r="X28" s="481" t="n"/>
       <c r="Y28" s="481" t="n"/>
@@ -6788,15 +6855,23 @@
       <c r="AN28" s="486" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="264">
-      <c r="A29" s="510">
-        <f>ROW()-ROW($A$17)+1</f>
+      <c r="A29" s="507">
+        <f>ROW()-ROW($A$18)+1</f>
         <v/>
       </c>
       <c r="B29" s="489" t="n"/>
-      <c r="C29" s="511" t="n"/>
+      <c r="C29" s="508" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
       <c r="D29" s="488" t="n"/>
       <c r="E29" s="489" t="n"/>
-      <c r="F29" s="512" t="n"/>
+      <c r="F29" s="509" t="inlineStr">
+        <is>
+          <t>Run condition after tool change is explicit.</t>
+        </is>
+      </c>
       <c r="G29" s="488" t="n"/>
       <c r="H29" s="488" t="n"/>
       <c r="I29" s="488" t="n"/>
@@ -6812,7 +6887,11 @@
       <c r="S29" s="488" t="n"/>
       <c r="T29" s="488" t="n"/>
       <c r="U29" s="489" t="n"/>
-      <c r="V29" s="511" t="n"/>
+      <c r="V29" s="510" t="inlineStr">
+        <is>
+          <t>Pass-to-run or hold decision visible.</t>
+        </is>
+      </c>
       <c r="W29" s="488" t="n"/>
       <c r="X29" s="488" t="n"/>
       <c r="Y29" s="488" t="n"/>
@@ -6822,18 +6901,18 @@
       <c r="AC29" s="488" t="n"/>
       <c r="AD29" s="488" t="n"/>
       <c r="AE29" s="489" t="n"/>
-      <c r="AF29" s="513" t="n"/>
+      <c r="AF29" s="511" t="n"/>
       <c r="AG29" s="488" t="n"/>
       <c r="AH29" s="488" t="n"/>
       <c r="AI29" s="489" t="n"/>
-      <c r="AJ29" s="514" t="n"/>
+      <c r="AJ29" s="512" t="n"/>
       <c r="AK29" s="488" t="n"/>
       <c r="AL29" s="488" t="n"/>
       <c r="AM29" s="488" t="n"/>
       <c r="AN29" s="493" t="n"/>
     </row>
     <row r="30" ht="4" customHeight="1" s="264">
-      <c r="A30" s="523" t="n"/>
+      <c r="A30" s="521" t="n"/>
       <c r="B30" s="26" t="n"/>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
@@ -6971,147 +7050,151 @@
       <c r="AN32" s="479" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="264">
-      <c r="A33" s="487" t="inlineStr">
+      <c r="A33" s="480" t="inlineStr">
         <is>
           <t>Open Conditions before Run</t>
         </is>
       </c>
-      <c r="B33" s="488" t="n"/>
-      <c r="C33" s="488" t="n"/>
-      <c r="D33" s="488" t="n"/>
-      <c r="E33" s="488" t="n"/>
-      <c r="F33" s="488" t="n"/>
-      <c r="G33" s="489" t="n"/>
-      <c r="H33" s="490" t="n"/>
-      <c r="I33" s="488" t="n"/>
-      <c r="J33" s="488" t="n"/>
-      <c r="K33" s="488" t="n"/>
-      <c r="L33" s="488" t="n"/>
-      <c r="M33" s="488" t="n"/>
-      <c r="N33" s="488" t="n"/>
-      <c r="O33" s="488" t="n"/>
-      <c r="P33" s="488" t="n"/>
-      <c r="Q33" s="488" t="n"/>
-      <c r="R33" s="488" t="n"/>
-      <c r="S33" s="488" t="n"/>
-      <c r="T33" s="489" t="n"/>
-      <c r="U33" s="491" t="inlineStr">
+      <c r="B33" s="481" t="n"/>
+      <c r="C33" s="481" t="n"/>
+      <c r="D33" s="481" t="n"/>
+      <c r="E33" s="481" t="n"/>
+      <c r="F33" s="481" t="n"/>
+      <c r="G33" s="482" t="n"/>
+      <c r="H33" s="483" t="n"/>
+      <c r="I33" s="481" t="n"/>
+      <c r="J33" s="481" t="n"/>
+      <c r="K33" s="481" t="n"/>
+      <c r="L33" s="481" t="n"/>
+      <c r="M33" s="481" t="n"/>
+      <c r="N33" s="481" t="n"/>
+      <c r="O33" s="481" t="n"/>
+      <c r="P33" s="481" t="n"/>
+      <c r="Q33" s="481" t="n"/>
+      <c r="R33" s="481" t="n"/>
+      <c r="S33" s="481" t="n"/>
+      <c r="T33" s="482" t="n"/>
+      <c r="U33" s="484" t="inlineStr">
         <is>
           <t>Action Owner / Deadline</t>
         </is>
       </c>
-      <c r="V33" s="488" t="n"/>
-      <c r="W33" s="488" t="n"/>
-      <c r="X33" s="488" t="n"/>
-      <c r="Y33" s="488" t="n"/>
-      <c r="Z33" s="488" t="n"/>
-      <c r="AA33" s="489" t="n"/>
-      <c r="AB33" s="492" t="n"/>
-      <c r="AC33" s="488" t="n"/>
-      <c r="AD33" s="488" t="n"/>
-      <c r="AE33" s="488" t="n"/>
-      <c r="AF33" s="488" t="n"/>
-      <c r="AG33" s="488" t="n"/>
-      <c r="AH33" s="488" t="n"/>
-      <c r="AI33" s="488" t="n"/>
-      <c r="AJ33" s="488" t="n"/>
-      <c r="AK33" s="488" t="n"/>
-      <c r="AL33" s="488" t="n"/>
-      <c r="AM33" s="488" t="n"/>
-      <c r="AN33" s="493" t="n"/>
+      <c r="V33" s="481" t="n"/>
+      <c r="W33" s="481" t="n"/>
+      <c r="X33" s="481" t="n"/>
+      <c r="Y33" s="481" t="n"/>
+      <c r="Z33" s="481" t="n"/>
+      <c r="AA33" s="482" t="n"/>
+      <c r="AB33" s="485" t="n"/>
+      <c r="AC33" s="481" t="n"/>
+      <c r="AD33" s="481" t="n"/>
+      <c r="AE33" s="481" t="n"/>
+      <c r="AF33" s="481" t="n"/>
+      <c r="AG33" s="481" t="n"/>
+      <c r="AH33" s="481" t="n"/>
+      <c r="AI33" s="481" t="n"/>
+      <c r="AJ33" s="481" t="n"/>
+      <c r="AK33" s="481" t="n"/>
+      <c r="AL33" s="481" t="n"/>
+      <c r="AM33" s="481" t="n"/>
+      <c r="AN33" s="486" t="n"/>
     </row>
-    <row r="34" ht="4" customHeight="1" s="264">
-      <c r="A34" s="523" t="n"/>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="26" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="26" t="n"/>
-      <c r="M34" s="26" t="n"/>
-      <c r="N34" s="26" t="n"/>
-      <c r="O34" s="26" t="n"/>
-      <c r="P34" s="26" t="n"/>
-      <c r="Q34" s="26" t="n"/>
-      <c r="R34" s="26" t="n"/>
-      <c r="S34" s="26" t="n"/>
-      <c r="T34" s="26" t="n"/>
-      <c r="U34" s="26" t="n"/>
-      <c r="V34" s="26" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="26" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="26" t="n"/>
-      <c r="AB34" s="26" t="n"/>
-      <c r="AC34" s="26" t="n"/>
-      <c r="AD34" s="26" t="n"/>
-      <c r="AE34" s="26" t="n"/>
-      <c r="AF34" s="26" t="n"/>
-      <c r="AG34" s="26" t="n"/>
-      <c r="AH34" s="26" t="n"/>
-      <c r="AI34" s="26" t="n"/>
-      <c r="AJ34" s="26" t="n"/>
-      <c r="AK34" s="26" t="n"/>
-      <c r="AL34" s="26" t="n"/>
-      <c r="AM34" s="26" t="n"/>
-      <c r="AN34" s="26" t="n"/>
+    <row r="34" ht="20" customHeight="1" s="264">
+      <c r="A34" s="487" t="inlineStr">
+        <is>
+          <t>Old Tool Disposition</t>
+        </is>
+      </c>
+      <c r="B34" s="488" t="n"/>
+      <c r="C34" s="488" t="n"/>
+      <c r="D34" s="488" t="n"/>
+      <c r="E34" s="488" t="n"/>
+      <c r="F34" s="488" t="n"/>
+      <c r="G34" s="489" t="n"/>
+      <c r="H34" s="490" t="n"/>
+      <c r="I34" s="488" t="n"/>
+      <c r="J34" s="488" t="n"/>
+      <c r="K34" s="488" t="n"/>
+      <c r="L34" s="488" t="n"/>
+      <c r="M34" s="488" t="n"/>
+      <c r="N34" s="488" t="n"/>
+      <c r="O34" s="488" t="n"/>
+      <c r="P34" s="488" t="n"/>
+      <c r="Q34" s="488" t="n"/>
+      <c r="R34" s="488" t="n"/>
+      <c r="S34" s="488" t="n"/>
+      <c r="T34" s="489" t="n"/>
+      <c r="U34" s="491" t="inlineStr">
+        <is>
+          <t>NCR Reference (if any)</t>
+        </is>
+      </c>
+      <c r="V34" s="488" t="n"/>
+      <c r="W34" s="488" t="n"/>
+      <c r="X34" s="488" t="n"/>
+      <c r="Y34" s="488" t="n"/>
+      <c r="Z34" s="488" t="n"/>
+      <c r="AA34" s="489" t="n"/>
+      <c r="AB34" s="492" t="n"/>
+      <c r="AC34" s="488" t="n"/>
+      <c r="AD34" s="488" t="n"/>
+      <c r="AE34" s="488" t="n"/>
+      <c r="AF34" s="488" t="n"/>
+      <c r="AG34" s="488" t="n"/>
+      <c r="AH34" s="488" t="n"/>
+      <c r="AI34" s="488" t="n"/>
+      <c r="AJ34" s="488" t="n"/>
+      <c r="AK34" s="488" t="n"/>
+      <c r="AL34" s="488" t="n"/>
+      <c r="AM34" s="488" t="n"/>
+      <c r="AN34" s="493" t="n"/>
     </row>
-    <row r="35" ht="17" customHeight="1" s="264">
-      <c r="A35" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  APPROVAL</t>
-        </is>
-      </c>
-      <c r="B35" s="471" t="n"/>
-      <c r="C35" s="471" t="n"/>
-      <c r="D35" s="471" t="n"/>
-      <c r="E35" s="471" t="n"/>
-      <c r="F35" s="471" t="n"/>
-      <c r="G35" s="471" t="n"/>
-      <c r="H35" s="471" t="n"/>
-      <c r="I35" s="471" t="n"/>
-      <c r="J35" s="471" t="n"/>
-      <c r="K35" s="471" t="n"/>
-      <c r="L35" s="471" t="n"/>
-      <c r="M35" s="471" t="n"/>
-      <c r="N35" s="471" t="n"/>
-      <c r="O35" s="471" t="n"/>
-      <c r="P35" s="471" t="n"/>
-      <c r="Q35" s="471" t="n"/>
-      <c r="R35" s="471" t="n"/>
-      <c r="S35" s="471" t="n"/>
-      <c r="T35" s="471" t="n"/>
-      <c r="U35" s="471" t="n"/>
-      <c r="V35" s="471" t="n"/>
-      <c r="W35" s="471" t="n"/>
-      <c r="X35" s="471" t="n"/>
-      <c r="Y35" s="471" t="n"/>
-      <c r="Z35" s="471" t="n"/>
-      <c r="AA35" s="471" t="n"/>
-      <c r="AB35" s="471" t="n"/>
-      <c r="AC35" s="471" t="n"/>
-      <c r="AD35" s="471" t="n"/>
-      <c r="AE35" s="471" t="n"/>
-      <c r="AF35" s="471" t="n"/>
-      <c r="AG35" s="471" t="n"/>
-      <c r="AH35" s="471" t="n"/>
-      <c r="AI35" s="471" t="n"/>
-      <c r="AJ35" s="471" t="n"/>
-      <c r="AK35" s="471" t="n"/>
-      <c r="AL35" s="471" t="n"/>
-      <c r="AM35" s="471" t="n"/>
-      <c r="AN35" s="472" t="n"/>
+    <row r="35" ht="4" customHeight="1" s="264">
+      <c r="A35" s="521" t="n"/>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="26" t="n"/>
+      <c r="G35" s="26" t="n"/>
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="26" t="n"/>
+      <c r="J35" s="26" t="n"/>
+      <c r="K35" s="26" t="n"/>
+      <c r="L35" s="26" t="n"/>
+      <c r="M35" s="26" t="n"/>
+      <c r="N35" s="26" t="n"/>
+      <c r="O35" s="26" t="n"/>
+      <c r="P35" s="26" t="n"/>
+      <c r="Q35" s="26" t="n"/>
+      <c r="R35" s="26" t="n"/>
+      <c r="S35" s="26" t="n"/>
+      <c r="T35" s="26" t="n"/>
+      <c r="U35" s="26" t="n"/>
+      <c r="V35" s="26" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="26" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="26" t="n"/>
+      <c r="AB35" s="26" t="n"/>
+      <c r="AC35" s="26" t="n"/>
+      <c r="AD35" s="26" t="n"/>
+      <c r="AE35" s="26" t="n"/>
+      <c r="AF35" s="26" t="n"/>
+      <c r="AG35" s="26" t="n"/>
+      <c r="AH35" s="26" t="n"/>
+      <c r="AI35" s="26" t="n"/>
+      <c r="AJ35" s="26" t="n"/>
+      <c r="AK35" s="26" t="n"/>
+      <c r="AL35" s="26" t="n"/>
+      <c r="AM35" s="26" t="n"/>
+      <c r="AN35" s="26" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1" s="264">
-      <c r="A36" s="515" t="inlineStr">
-        <is>
-          <t>Operator</t>
+      <c r="A36" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  APPROVAL</t>
         </is>
       </c>
       <c r="B36" s="471" t="n"/>
@@ -7125,12 +7208,8 @@
       <c r="J36" s="471" t="n"/>
       <c r="K36" s="471" t="n"/>
       <c r="L36" s="471" t="n"/>
-      <c r="M36" s="472" t="n"/>
-      <c r="N36" s="515" t="inlineStr">
-        <is>
-          <t>QC Verifier</t>
-        </is>
-      </c>
+      <c r="M36" s="471" t="n"/>
+      <c r="N36" s="471" t="n"/>
       <c r="O36" s="471" t="n"/>
       <c r="P36" s="471" t="n"/>
       <c r="Q36" s="471" t="n"/>
@@ -7142,12 +7221,8 @@
       <c r="W36" s="471" t="n"/>
       <c r="X36" s="471" t="n"/>
       <c r="Y36" s="471" t="n"/>
-      <c r="Z36" s="472" t="n"/>
-      <c r="AA36" s="515" t="inlineStr">
-        <is>
-          <t>Production Supervisor</t>
-        </is>
-      </c>
+      <c r="Z36" s="471" t="n"/>
+      <c r="AA36" s="471" t="n"/>
       <c r="AB36" s="471" t="n"/>
       <c r="AC36" s="471" t="n"/>
       <c r="AD36" s="471" t="n"/>
@@ -7162,222 +7237,277 @@
       <c r="AM36" s="471" t="n"/>
       <c r="AN36" s="472" t="n"/>
     </row>
-    <row r="37" ht="26" customHeight="1" s="264">
-      <c r="A37" s="516" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="B37" s="517" t="n"/>
-      <c r="C37" s="517" t="n"/>
-      <c r="D37" s="517" t="n"/>
-      <c r="E37" s="517" t="n"/>
-      <c r="F37" s="517" t="n"/>
-      <c r="G37" s="517" t="n"/>
-      <c r="H37" s="517" t="n"/>
-      <c r="I37" s="517" t="n"/>
-      <c r="J37" s="517" t="n"/>
-      <c r="K37" s="517" t="n"/>
-      <c r="L37" s="517" t="n"/>
-      <c r="M37" s="518" t="n"/>
-      <c r="N37" s="516" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="O37" s="517" t="n"/>
-      <c r="P37" s="517" t="n"/>
-      <c r="Q37" s="517" t="n"/>
-      <c r="R37" s="517" t="n"/>
-      <c r="S37" s="517" t="n"/>
-      <c r="T37" s="517" t="n"/>
-      <c r="U37" s="517" t="n"/>
-      <c r="V37" s="517" t="n"/>
-      <c r="W37" s="517" t="n"/>
-      <c r="X37" s="517" t="n"/>
-      <c r="Y37" s="517" t="n"/>
-      <c r="Z37" s="518" t="n"/>
-      <c r="AA37" s="516" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="AB37" s="517" t="n"/>
-      <c r="AC37" s="517" t="n"/>
-      <c r="AD37" s="517" t="n"/>
-      <c r="AE37" s="517" t="n"/>
-      <c r="AF37" s="517" t="n"/>
-      <c r="AG37" s="517" t="n"/>
-      <c r="AH37" s="517" t="n"/>
-      <c r="AI37" s="517" t="n"/>
-      <c r="AJ37" s="517" t="n"/>
-      <c r="AK37" s="517" t="n"/>
-      <c r="AL37" s="517" t="n"/>
-      <c r="AM37" s="517" t="n"/>
-      <c r="AN37" s="518" t="n"/>
+    <row r="37" ht="17" customHeight="1" s="264">
+      <c r="A37" s="513" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="B37" s="471" t="n"/>
+      <c r="C37" s="471" t="n"/>
+      <c r="D37" s="471" t="n"/>
+      <c r="E37" s="471" t="n"/>
+      <c r="F37" s="471" t="n"/>
+      <c r="G37" s="471" t="n"/>
+      <c r="H37" s="471" t="n"/>
+      <c r="I37" s="471" t="n"/>
+      <c r="J37" s="471" t="n"/>
+      <c r="K37" s="471" t="n"/>
+      <c r="L37" s="471" t="n"/>
+      <c r="M37" s="472" t="n"/>
+      <c r="N37" s="513" t="inlineStr">
+        <is>
+          <t>QC Verifier</t>
+        </is>
+      </c>
+      <c r="O37" s="471" t="n"/>
+      <c r="P37" s="471" t="n"/>
+      <c r="Q37" s="471" t="n"/>
+      <c r="R37" s="471" t="n"/>
+      <c r="S37" s="471" t="n"/>
+      <c r="T37" s="471" t="n"/>
+      <c r="U37" s="471" t="n"/>
+      <c r="V37" s="471" t="n"/>
+      <c r="W37" s="471" t="n"/>
+      <c r="X37" s="471" t="n"/>
+      <c r="Y37" s="471" t="n"/>
+      <c r="Z37" s="472" t="n"/>
+      <c r="AA37" s="513" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="AB37" s="471" t="n"/>
+      <c r="AC37" s="471" t="n"/>
+      <c r="AD37" s="471" t="n"/>
+      <c r="AE37" s="471" t="n"/>
+      <c r="AF37" s="471" t="n"/>
+      <c r="AG37" s="471" t="n"/>
+      <c r="AH37" s="471" t="n"/>
+      <c r="AI37" s="471" t="n"/>
+      <c r="AJ37" s="471" t="n"/>
+      <c r="AK37" s="471" t="n"/>
+      <c r="AL37" s="471" t="n"/>
+      <c r="AM37" s="471" t="n"/>
+      <c r="AN37" s="472" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1" s="264">
-      <c r="A38" s="519" t="n"/>
-      <c r="M38" s="520" t="n"/>
-      <c r="N38" s="519" t="n"/>
-      <c r="Z38" s="520" t="n"/>
-      <c r="AA38" s="519" t="n"/>
-      <c r="AN38" s="520" t="n"/>
+      <c r="A38" s="514" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="B38" s="515" t="n"/>
+      <c r="C38" s="515" t="n"/>
+      <c r="D38" s="515" t="n"/>
+      <c r="E38" s="515" t="n"/>
+      <c r="F38" s="515" t="n"/>
+      <c r="G38" s="515" t="n"/>
+      <c r="H38" s="515" t="n"/>
+      <c r="I38" s="515" t="n"/>
+      <c r="J38" s="515" t="n"/>
+      <c r="K38" s="515" t="n"/>
+      <c r="L38" s="515" t="n"/>
+      <c r="M38" s="516" t="n"/>
+      <c r="N38" s="514" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="O38" s="515" t="n"/>
+      <c r="P38" s="515" t="n"/>
+      <c r="Q38" s="515" t="n"/>
+      <c r="R38" s="515" t="n"/>
+      <c r="S38" s="515" t="n"/>
+      <c r="T38" s="515" t="n"/>
+      <c r="U38" s="515" t="n"/>
+      <c r="V38" s="515" t="n"/>
+      <c r="W38" s="515" t="n"/>
+      <c r="X38" s="515" t="n"/>
+      <c r="Y38" s="515" t="n"/>
+      <c r="Z38" s="516" t="n"/>
+      <c r="AA38" s="514" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="AB38" s="515" t="n"/>
+      <c r="AC38" s="515" t="n"/>
+      <c r="AD38" s="515" t="n"/>
+      <c r="AE38" s="515" t="n"/>
+      <c r="AF38" s="515" t="n"/>
+      <c r="AG38" s="515" t="n"/>
+      <c r="AH38" s="515" t="n"/>
+      <c r="AI38" s="515" t="n"/>
+      <c r="AJ38" s="515" t="n"/>
+      <c r="AK38" s="515" t="n"/>
+      <c r="AL38" s="515" t="n"/>
+      <c r="AM38" s="515" t="n"/>
+      <c r="AN38" s="516" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1" s="264">
-      <c r="A39" s="521" t="n"/>
-      <c r="B39" s="488" t="n"/>
-      <c r="C39" s="488" t="n"/>
-      <c r="D39" s="488" t="n"/>
-      <c r="E39" s="488" t="n"/>
-      <c r="F39" s="488" t="n"/>
-      <c r="G39" s="488" t="n"/>
-      <c r="H39" s="488" t="n"/>
-      <c r="I39" s="488" t="n"/>
-      <c r="J39" s="488" t="n"/>
-      <c r="K39" s="488" t="n"/>
-      <c r="L39" s="488" t="n"/>
-      <c r="M39" s="493" t="n"/>
-      <c r="N39" s="521" t="n"/>
-      <c r="O39" s="488" t="n"/>
-      <c r="P39" s="488" t="n"/>
-      <c r="Q39" s="488" t="n"/>
-      <c r="R39" s="488" t="n"/>
-      <c r="S39" s="488" t="n"/>
-      <c r="T39" s="488" t="n"/>
-      <c r="U39" s="488" t="n"/>
-      <c r="V39" s="488" t="n"/>
-      <c r="W39" s="488" t="n"/>
-      <c r="X39" s="488" t="n"/>
-      <c r="Y39" s="488" t="n"/>
-      <c r="Z39" s="493" t="n"/>
-      <c r="AA39" s="521" t="n"/>
-      <c r="AB39" s="488" t="n"/>
-      <c r="AC39" s="488" t="n"/>
-      <c r="AD39" s="488" t="n"/>
-      <c r="AE39" s="488" t="n"/>
-      <c r="AF39" s="488" t="n"/>
-      <c r="AG39" s="488" t="n"/>
-      <c r="AH39" s="488" t="n"/>
-      <c r="AI39" s="488" t="n"/>
-      <c r="AJ39" s="488" t="n"/>
-      <c r="AK39" s="488" t="n"/>
-      <c r="AL39" s="488" t="n"/>
-      <c r="AM39" s="488" t="n"/>
-      <c r="AN39" s="493" t="n"/>
+      <c r="A39" s="517" t="n"/>
+      <c r="M39" s="518" t="n"/>
+      <c r="N39" s="517" t="n"/>
+      <c r="Z39" s="518" t="n"/>
+      <c r="AA39" s="517" t="n"/>
+      <c r="AN39" s="518" t="n"/>
     </row>
-    <row r="40" ht="4" customHeight="1" s="264">
-      <c r="A40" s="523" t="n"/>
-      <c r="B40" s="26" t="n"/>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="26" t="n"/>
-      <c r="K40" s="26" t="n"/>
-      <c r="L40" s="26" t="n"/>
-      <c r="M40" s="26" t="n"/>
-      <c r="N40" s="26" t="n"/>
-      <c r="O40" s="26" t="n"/>
-      <c r="P40" s="26" t="n"/>
-      <c r="Q40" s="26" t="n"/>
-      <c r="R40" s="26" t="n"/>
-      <c r="S40" s="26" t="n"/>
-      <c r="T40" s="26" t="n"/>
-      <c r="U40" s="26" t="n"/>
-      <c r="V40" s="26" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="26" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="26" t="n"/>
-      <c r="AB40" s="26" t="n"/>
-      <c r="AC40" s="26" t="n"/>
-      <c r="AD40" s="26" t="n"/>
-      <c r="AE40" s="26" t="n"/>
-      <c r="AF40" s="26" t="n"/>
-      <c r="AG40" s="26" t="n"/>
-      <c r="AH40" s="26" t="n"/>
-      <c r="AI40" s="26" t="n"/>
-      <c r="AJ40" s="26" t="n"/>
-      <c r="AK40" s="26" t="n"/>
-      <c r="AL40" s="26" t="n"/>
-      <c r="AM40" s="26" t="n"/>
-      <c r="AN40" s="26" t="n"/>
+    <row r="40" ht="26" customHeight="1" s="264">
+      <c r="A40" s="519" t="n"/>
+      <c r="B40" s="488" t="n"/>
+      <c r="C40" s="488" t="n"/>
+      <c r="D40" s="488" t="n"/>
+      <c r="E40" s="488" t="n"/>
+      <c r="F40" s="488" t="n"/>
+      <c r="G40" s="488" t="n"/>
+      <c r="H40" s="488" t="n"/>
+      <c r="I40" s="488" t="n"/>
+      <c r="J40" s="488" t="n"/>
+      <c r="K40" s="488" t="n"/>
+      <c r="L40" s="488" t="n"/>
+      <c r="M40" s="493" t="n"/>
+      <c r="N40" s="519" t="n"/>
+      <c r="O40" s="488" t="n"/>
+      <c r="P40" s="488" t="n"/>
+      <c r="Q40" s="488" t="n"/>
+      <c r="R40" s="488" t="n"/>
+      <c r="S40" s="488" t="n"/>
+      <c r="T40" s="488" t="n"/>
+      <c r="U40" s="488" t="n"/>
+      <c r="V40" s="488" t="n"/>
+      <c r="W40" s="488" t="n"/>
+      <c r="X40" s="488" t="n"/>
+      <c r="Y40" s="488" t="n"/>
+      <c r="Z40" s="493" t="n"/>
+      <c r="AA40" s="519" t="n"/>
+      <c r="AB40" s="488" t="n"/>
+      <c r="AC40" s="488" t="n"/>
+      <c r="AD40" s="488" t="n"/>
+      <c r="AE40" s="488" t="n"/>
+      <c r="AF40" s="488" t="n"/>
+      <c r="AG40" s="488" t="n"/>
+      <c r="AH40" s="488" t="n"/>
+      <c r="AI40" s="488" t="n"/>
+      <c r="AJ40" s="488" t="n"/>
+      <c r="AK40" s="488" t="n"/>
+      <c r="AL40" s="488" t="n"/>
+      <c r="AM40" s="488" t="n"/>
+      <c r="AN40" s="493" t="n"/>
     </row>
-    <row r="41" ht="24" customHeight="1" s="264">
-      <c r="A41" s="522" t="inlineStr">
-        <is>
-          <t>NOTICE — A tool change without first-piece verification (FRM-622) is a process violation. Ref: SOP-503 / FRM-513. Retain: 7 years.</t>
-        </is>
-      </c>
-      <c r="B41" s="471" t="n"/>
-      <c r="C41" s="471" t="n"/>
-      <c r="D41" s="471" t="n"/>
-      <c r="E41" s="471" t="n"/>
-      <c r="F41" s="471" t="n"/>
-      <c r="G41" s="471" t="n"/>
-      <c r="H41" s="471" t="n"/>
-      <c r="I41" s="471" t="n"/>
-      <c r="J41" s="471" t="n"/>
-      <c r="K41" s="471" t="n"/>
-      <c r="L41" s="471" t="n"/>
-      <c r="M41" s="471" t="n"/>
-      <c r="N41" s="471" t="n"/>
-      <c r="O41" s="471" t="n"/>
-      <c r="P41" s="471" t="n"/>
-      <c r="Q41" s="471" t="n"/>
-      <c r="R41" s="471" t="n"/>
-      <c r="S41" s="471" t="n"/>
-      <c r="T41" s="471" t="n"/>
-      <c r="U41" s="471" t="n"/>
-      <c r="V41" s="471" t="n"/>
-      <c r="W41" s="471" t="n"/>
-      <c r="X41" s="471" t="n"/>
-      <c r="Y41" s="471" t="n"/>
-      <c r="Z41" s="471" t="n"/>
-      <c r="AA41" s="471" t="n"/>
-      <c r="AB41" s="471" t="n"/>
-      <c r="AC41" s="471" t="n"/>
-      <c r="AD41" s="471" t="n"/>
-      <c r="AE41" s="471" t="n"/>
-      <c r="AF41" s="471" t="n"/>
-      <c r="AG41" s="471" t="n"/>
-      <c r="AH41" s="471" t="n"/>
-      <c r="AI41" s="471" t="n"/>
-      <c r="AJ41" s="471" t="n"/>
-      <c r="AK41" s="471" t="n"/>
-      <c r="AL41" s="471" t="n"/>
-      <c r="AM41" s="471" t="n"/>
-      <c r="AN41" s="472" t="n"/>
+    <row r="41" ht="4" customHeight="1" s="264">
+      <c r="A41" s="521" t="n"/>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
+      <c r="M41" s="26" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="26" t="n"/>
+      <c r="V41" s="26" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="26" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="26" t="n"/>
+      <c r="AC41" s="26" t="n"/>
+      <c r="AD41" s="26" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="26" t="n"/>
+      <c r="AG41" s="26" t="n"/>
+      <c r="AH41" s="26" t="n"/>
+      <c r="AI41" s="26" t="n"/>
+      <c r="AJ41" s="26" t="n"/>
+      <c r="AK41" s="26" t="n"/>
+      <c r="AL41" s="26" t="n"/>
+      <c r="AM41" s="26" t="n"/>
+      <c r="AN41" s="26" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" s="264">
+      <c r="A42" s="520" t="inlineStr">
+        <is>
+          <t>NOTICE — A tool change without first-piece verification (FRM-622) is a process violation. Ref: SOP-503 / FRM-513. Retain: 7 years. Enter data only in white input cells. Do not add, delete or resize columns/rows.</t>
+        </is>
+      </c>
+      <c r="B42" s="471" t="n"/>
+      <c r="C42" s="471" t="n"/>
+      <c r="D42" s="471" t="n"/>
+      <c r="E42" s="471" t="n"/>
+      <c r="F42" s="471" t="n"/>
+      <c r="G42" s="471" t="n"/>
+      <c r="H42" s="471" t="n"/>
+      <c r="I42" s="471" t="n"/>
+      <c r="J42" s="471" t="n"/>
+      <c r="K42" s="471" t="n"/>
+      <c r="L42" s="471" t="n"/>
+      <c r="M42" s="471" t="n"/>
+      <c r="N42" s="471" t="n"/>
+      <c r="O42" s="471" t="n"/>
+      <c r="P42" s="471" t="n"/>
+      <c r="Q42" s="471" t="n"/>
+      <c r="R42" s="471" t="n"/>
+      <c r="S42" s="471" t="n"/>
+      <c r="T42" s="471" t="n"/>
+      <c r="U42" s="471" t="n"/>
+      <c r="V42" s="471" t="n"/>
+      <c r="W42" s="471" t="n"/>
+      <c r="X42" s="471" t="n"/>
+      <c r="Y42" s="471" t="n"/>
+      <c r="Z42" s="471" t="n"/>
+      <c r="AA42" s="471" t="n"/>
+      <c r="AB42" s="471" t="n"/>
+      <c r="AC42" s="471" t="n"/>
+      <c r="AD42" s="471" t="n"/>
+      <c r="AE42" s="471" t="n"/>
+      <c r="AF42" s="471" t="n"/>
+      <c r="AG42" s="471" t="n"/>
+      <c r="AH42" s="471" t="n"/>
+      <c r="AI42" s="471" t="n"/>
+      <c r="AJ42" s="471" t="n"/>
+      <c r="AK42" s="471" t="n"/>
+      <c r="AL42" s="471" t="n"/>
+      <c r="AM42" s="471" t="n"/>
+      <c r="AN42" s="472" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="142">
+  <mergeCells count="144">
     <mergeCell ref="U33:AA33"/>
+    <mergeCell ref="N38:Z40"/>
     <mergeCell ref="F23:U23"/>
     <mergeCell ref="AF23:AI23"/>
     <mergeCell ref="AE6:AH6"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A14:AN14"/>
     <mergeCell ref="H33:T33"/>
     <mergeCell ref="V22:AE22"/>
+    <mergeCell ref="U14:AA14"/>
+    <mergeCell ref="AB34:AN34"/>
     <mergeCell ref="AF22:AI22"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="AE4:AH4"/>
     <mergeCell ref="AF18:AI18"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="U9:AA9"/>
-    <mergeCell ref="N36:Z36"/>
     <mergeCell ref="V21:AE21"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A40:AN40"/>
     <mergeCell ref="AJ18:AN18"/>
     <mergeCell ref="F19:U19"/>
     <mergeCell ref="V23:AE23"/>
+    <mergeCell ref="AB14:AN14"/>
     <mergeCell ref="H9:T9"/>
     <mergeCell ref="I2:AD4"/>
     <mergeCell ref="C18:E18"/>
@@ -7385,9 +7515,9 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="F20:U20"/>
     <mergeCell ref="U32:AA32"/>
-    <mergeCell ref="N37:Z39"/>
     <mergeCell ref="A2:H6"/>
     <mergeCell ref="AJ20:AN20"/>
+    <mergeCell ref="A16:AN16"/>
     <mergeCell ref="U13:AA13"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="AJ29:AN29"/>
@@ -7412,9 +7542,10 @@
     <mergeCell ref="AB10:AN10"/>
     <mergeCell ref="AF27:AI27"/>
     <mergeCell ref="AB33:AN33"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="V17:AE17"/>
+    <mergeCell ref="U34:AA34"/>
     <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="AA36:AN36"/>
     <mergeCell ref="AI3:AN3"/>
     <mergeCell ref="A31:AN31"/>
     <mergeCell ref="H10:T10"/>
@@ -7422,36 +7553,36 @@
     <mergeCell ref="A15:AN15"/>
     <mergeCell ref="AI5:AN5"/>
     <mergeCell ref="V20:AE20"/>
+    <mergeCell ref="H34:T34"/>
     <mergeCell ref="V29:AE29"/>
-    <mergeCell ref="AF16:AI16"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="AF25:AI25"/>
     <mergeCell ref="AJ26:AN26"/>
     <mergeCell ref="F18:U18"/>
     <mergeCell ref="A7:AN7"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="AJ16:AN16"/>
     <mergeCell ref="A41:AN41"/>
     <mergeCell ref="AJ25:AN25"/>
     <mergeCell ref="U12:AA12"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="AB12:AN12"/>
     <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="C16:E16"/>
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="F22:U22"/>
     <mergeCell ref="V26:AE26"/>
     <mergeCell ref="H12:T12"/>
+    <mergeCell ref="A42:AN42"/>
     <mergeCell ref="AB13:AN13"/>
-    <mergeCell ref="V16:AE16"/>
+    <mergeCell ref="AA38:AN40"/>
     <mergeCell ref="AF28:AI28"/>
     <mergeCell ref="A35:AN35"/>
+    <mergeCell ref="H14:T14"/>
     <mergeCell ref="V18:AE18"/>
     <mergeCell ref="I6:AD6"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="AI2:AN2"/>
-    <mergeCell ref="A36:M36"/>
     <mergeCell ref="A30:AN30"/>
     <mergeCell ref="AB32:AN32"/>
     <mergeCell ref="AE3:AH3"/>
@@ -7461,10 +7592,10 @@
     <mergeCell ref="U11:AA11"/>
     <mergeCell ref="F21:U21"/>
     <mergeCell ref="V28:AE28"/>
+    <mergeCell ref="A37:M37"/>
     <mergeCell ref="AB9:AN9"/>
     <mergeCell ref="F26:U26"/>
     <mergeCell ref="H11:T11"/>
-    <mergeCell ref="A37:M39"/>
     <mergeCell ref="AB11:AN11"/>
     <mergeCell ref="AI6:AN6"/>
     <mergeCell ref="A24:B24"/>
@@ -7472,25 +7603,25 @@
     <mergeCell ref="F27:U27"/>
     <mergeCell ref="AJ27:AN27"/>
     <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="A38:M40"/>
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="AJ17:AN17"/>
     <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="AA37:AN39"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="AA37:AN37"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="AJ19:AN19"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AJ28:AN28"/>
     <mergeCell ref="F29:U29"/>
-    <mergeCell ref="F16:U16"/>
     <mergeCell ref="F25:U25"/>
-    <mergeCell ref="A34:AN34"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="N37:Z37"/>
     <mergeCell ref="AF29:AI29"/>
     <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="A36:AN36"/>
     <mergeCell ref="V24:AE24"/>
     <mergeCell ref="V19:AE19"/>
     <mergeCell ref="A20:B20"/>
@@ -7499,7 +7630,7 @@
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A33:G33"/>
   </mergeCells>
-  <conditionalFormatting sqref="AF17:AF29">
+  <conditionalFormatting sqref="AF18:AF29">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -7511,13 +7642,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=LISTS!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
